--- a/Pricing Logic/modules/uploads/module_4_1126.xlsx
+++ b/Pricing Logic/modules/uploads/module_4_1126.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="10">
   <si>
     <t>Product ID</t>
   </si>
@@ -37,7 +37,10 @@
     <t>Tags</t>
   </si>
   <si>
-    <t>بيبسى كانز جيب - 240 مل</t>
+    <t>بيبسي هضبه - 250 مل</t>
+  </si>
+  <si>
+    <t>ميرندا برتقال هضبه - 250 مل</t>
   </si>
   <si>
     <t>YES</t>
@@ -398,7 +401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -426,7 +429,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>434</v>
+        <v>25958</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
@@ -435,10 +438,27 @@
         <v>2</v>
       </c>
       <c r="D2">
-        <v>301.75</v>
+        <v>107.5</v>
       </c>
       <c r="E2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>25960</v>
+      </c>
+      <c r="B3" t="s">
         <v>8</v>
+      </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
+      <c r="D3">
+        <v>107.5</v>
+      </c>
+      <c r="E3" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/Pricing Logic/modules/uploads/module_4_1126.xlsx
+++ b/Pricing Logic/modules/uploads/module_4_1126.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>Product ID</t>
   </si>
@@ -37,10 +37,7 @@
     <t>Tags</t>
   </si>
   <si>
-    <t>بيبسي هضبه - 250 مل</t>
-  </si>
-  <si>
-    <t>ميرندا برتقال هضبه - 250 مل</t>
+    <t>بيبسى تربو - 390 مل</t>
   </si>
   <si>
     <t>YES</t>
@@ -401,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -429,7 +426,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>25958</v>
+        <v>593</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
@@ -438,27 +435,10 @@
         <v>2</v>
       </c>
       <c r="D2">
-        <v>107.5</v>
+        <v>130</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>25960</v>
-      </c>
-      <c r="B3" t="s">
         <v>8</v>
-      </c>
-      <c r="C3">
-        <v>2</v>
-      </c>
-      <c r="D3">
-        <v>107.5</v>
-      </c>
-      <c r="E3" t="s">
-        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/Pricing Logic/modules/uploads/module_4_1126.xlsx
+++ b/Pricing Logic/modules/uploads/module_4_1126.xlsx
@@ -37,7 +37,7 @@
     <t>Tags</t>
   </si>
   <si>
-    <t>بيبسى تربو - 390 مل</t>
+    <t>فيبا سائل أطباق تفاح- 520 جم</t>
   </si>
   <si>
     <t>YES</t>
@@ -426,16 +426,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>593</v>
+        <v>1742</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
       </c>
       <c r="C2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D2">
-        <v>130</v>
+        <v>177</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>

--- a/Pricing Logic/modules/uploads/module_4_1126.xlsx
+++ b/Pricing Logic/modules/uploads/module_4_1126.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="10">
   <si>
     <t>Product ID</t>
   </si>
@@ -37,7 +37,10 @@
     <t>Tags</t>
   </si>
   <si>
-    <t>فيبا سائل أطباق تفاح- 520 جم</t>
+    <t>مكرونة كايرو اسباجتى - 400 جم</t>
+  </si>
+  <si>
+    <t>مولبد حماية ضد البكتريا طويل 14 + 2  فوطة مجانا - 16 فوطة</t>
   </si>
   <si>
     <t>YES</t>
@@ -398,7 +401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -426,7 +429,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>1742</v>
+        <v>5851</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
@@ -435,10 +438,44 @@
         <v>1</v>
       </c>
       <c r="D2">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="E2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>13243</v>
+      </c>
+      <c r="B3" t="s">
         <v>8</v>
+      </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
+      <c r="D3">
+        <v>72.5</v>
+      </c>
+      <c r="E3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>13243</v>
+      </c>
+      <c r="B4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>580</v>
+      </c>
+      <c r="E4" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/Pricing Logic/modules/uploads/module_4_1126.xlsx
+++ b/Pricing Logic/modules/uploads/module_4_1126.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="12">
   <si>
     <t>Product ID</t>
   </si>
@@ -37,10 +37,16 @@
     <t>Tags</t>
   </si>
   <si>
-    <t>مكرونة كايرو اسباجتى - 400 جم</t>
-  </si>
-  <si>
-    <t>مولبد حماية ضد البكتريا طويل 14 + 2  فوطة مجانا - 16 فوطة</t>
+    <t>هارفست صلصة شرينك ٢ برطمان خصم   15 % --- 320 جم</t>
+  </si>
+  <si>
+    <t>بن عبد المعبود محوج فاتح سوفت - 25 جم</t>
+  </si>
+  <si>
+    <t>كل يوم عصير تفاح - 200 مل</t>
+  </si>
+  <si>
+    <t>ماكسـي ليمون - 2 لتر</t>
   </si>
   <si>
     <t>YES</t>
@@ -401,7 +407,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -429,53 +435,87 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>5851</v>
+        <v>5080</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2">
-        <v>183</v>
+        <v>245.5</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>13243</v>
+        <v>6627</v>
       </c>
       <c r="B3" t="s">
         <v>8</v>
       </c>
       <c r="C3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D3">
-        <v>72.5</v>
+        <v>2167.5</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>13243</v>
+        <v>6627</v>
       </c>
       <c r="B4" t="s">
         <v>8</v>
       </c>
       <c r="C4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D4">
-        <v>580</v>
+        <v>361.25</v>
       </c>
       <c r="E4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>11837</v>
+      </c>
+      <c r="B5" t="s">
         <v>9</v>
+      </c>
+      <c r="C5">
+        <v>2</v>
+      </c>
+      <c r="D5">
+        <v>113.5</v>
+      </c>
+      <c r="E5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>24756</v>
+      </c>
+      <c r="B6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6">
+        <v>2</v>
+      </c>
+      <c r="D6">
+        <v>151.5</v>
+      </c>
+      <c r="E6" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/Pricing Logic/modules/uploads/module_4_1126.xlsx
+++ b/Pricing Logic/modules/uploads/module_4_1126.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="9">
   <si>
     <t>Product ID</t>
   </si>
@@ -37,16 +37,7 @@
     <t>Tags</t>
   </si>
   <si>
-    <t>هارفست صلصة شرينك ٢ برطمان خصم   15 % --- 320 جم</t>
-  </si>
-  <si>
-    <t>بن عبد المعبود محوج فاتح سوفت - 25 جم</t>
-  </si>
-  <si>
-    <t>كل يوم عصير تفاح - 200 مل</t>
-  </si>
-  <si>
-    <t>ماكسـي ليمون - 2 لتر</t>
+    <t>صابون كامى كلاسيك -- 110 جم</t>
   </si>
   <si>
     <t>YES</t>
@@ -407,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -435,7 +426,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>5080</v>
+        <v>8285</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
@@ -444,78 +435,27 @@
         <v>2</v>
       </c>
       <c r="D2">
-        <v>245.5</v>
+        <v>61.25</v>
       </c>
       <c r="E2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>6627</v>
+        <v>8285</v>
       </c>
       <c r="B3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C3">
         <v>1</v>
       </c>
       <c r="D3">
-        <v>2167.5</v>
+        <v>735</v>
       </c>
       <c r="E3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>6627</v>
-      </c>
-      <c r="B4" t="s">
         <v>8</v>
-      </c>
-      <c r="C4">
-        <v>3</v>
-      </c>
-      <c r="D4">
-        <v>361.25</v>
-      </c>
-      <c r="E4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>11837</v>
-      </c>
-      <c r="B5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C5">
-        <v>2</v>
-      </c>
-      <c r="D5">
-        <v>113.5</v>
-      </c>
-      <c r="E5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>24756</v>
-      </c>
-      <c r="B6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6">
-        <v>2</v>
-      </c>
-      <c r="D6">
-        <v>151.5</v>
-      </c>
-      <c r="E6" t="s">
-        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/Pricing Logic/modules/uploads/module_4_1126.xlsx
+++ b/Pricing Logic/modules/uploads/module_4_1126.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="11">
   <si>
     <t>Product ID</t>
   </si>
@@ -37,7 +37,13 @@
     <t>Tags</t>
   </si>
   <si>
-    <t>زيووو شرائح كيرليى طماطم وريحان - 5 جنية</t>
+    <t>أولويز ماكسى سميكة ناعمة حساس بلمسة الألوڤيرا طويلة  +2 فوطة مجانا 16 فوطة</t>
+  </si>
+  <si>
+    <t>زيت ثمرات خليط - 550 مل</t>
+  </si>
+  <si>
+    <t>مولبد حماية ضد البكتريا طويل جدا 12 + 2 فوطة مجانا - 14 فوطة</t>
   </si>
   <si>
     <t>YES</t>
@@ -398,7 +404,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -426,7 +432,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>12347</v>
+        <v>9840</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
@@ -435,10 +441,78 @@
         <v>1</v>
       </c>
       <c r="D2">
-        <v>46.5</v>
+        <v>592</v>
       </c>
       <c r="E2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>9840</v>
+      </c>
+      <c r="B3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3">
+        <v>25</v>
+      </c>
+      <c r="D3">
+        <v>37</v>
+      </c>
+      <c r="E3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>12925</v>
+      </c>
+      <c r="B4" t="s">
         <v>8</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>468</v>
+      </c>
+      <c r="E4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>13244</v>
+      </c>
+      <c r="B5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5">
+        <v>2</v>
+      </c>
+      <c r="D5">
+        <v>72.25</v>
+      </c>
+      <c r="E5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>13244</v>
+      </c>
+      <c r="B6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6">
+        <v>578</v>
+      </c>
+      <c r="E6" t="s">
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/Pricing Logic/modules/uploads/module_4_1126.xlsx
+++ b/Pricing Logic/modules/uploads/module_4_1126.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="24">
   <si>
     <t>Product ID</t>
   </si>
@@ -37,13 +37,52 @@
     <t>Tags</t>
   </si>
   <si>
-    <t>أولويز ماكسى سميكة ناعمة حساس بلمسة الألوڤيرا طويلة  +2 فوطة مجانا 16 فوطة</t>
-  </si>
-  <si>
-    <t>زيت ثمرات خليط - 550 مل</t>
-  </si>
-  <si>
-    <t>مولبد حماية ضد البكتريا طويل جدا 12 + 2 فوطة مجانا - 14 فوطة</t>
+    <t>باندا مثلثات - 16 قطعه</t>
+  </si>
+  <si>
+    <t>باندا جورمية مثلثات - 8 قطعه</t>
+  </si>
+  <si>
+    <t>باندا جورمية مثلثات - 16 قطعه</t>
+  </si>
+  <si>
+    <t>باندا جورمية جبنة مربعات ب القشطة - 6 قطعه</t>
+  </si>
+  <si>
+    <t>ديرى مثلثات - 16 قطعه</t>
+  </si>
+  <si>
+    <t>جبنة باندا فيتا  - 500 جم</t>
+  </si>
+  <si>
+    <t>جبنة باندا رومى - 250 جم</t>
+  </si>
+  <si>
+    <t>جبنة باندا شيدر - 500 جم</t>
+  </si>
+  <si>
+    <t>جبنة باندا رومى - 500 جم</t>
+  </si>
+  <si>
+    <t>جبنة باندا شيدر  - 125 جم</t>
+  </si>
+  <si>
+    <t>جبنة باندا بسطرمة  - 125 جم</t>
+  </si>
+  <si>
+    <t>جبنة ديرى فيتا بلس  - 125 جم</t>
+  </si>
+  <si>
+    <t>جبنة ديرى فيتا  - 250 جم</t>
+  </si>
+  <si>
+    <t>جبنة ديرى فيتا بلس - 500 جم</t>
+  </si>
+  <si>
+    <t>جبنة باندا فيتا 250 جرام</t>
+  </si>
+  <si>
+    <t>جبنة باندا فيتا 125 جرام</t>
   </si>
   <si>
     <t>YES</t>
@@ -404,7 +443,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -432,7 +471,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>9840</v>
+        <v>21705</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
@@ -441,66 +480,66 @@
         <v>1</v>
       </c>
       <c r="D2">
-        <v>592</v>
+        <v>870</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>9840</v>
+        <v>21705</v>
       </c>
       <c r="B3" t="s">
         <v>7</v>
       </c>
       <c r="C3">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="D3">
-        <v>37</v>
+        <v>36.25</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>12925</v>
+        <v>21706</v>
       </c>
       <c r="B4" t="s">
         <v>8</v>
       </c>
       <c r="C4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D4">
-        <v>468</v>
+        <v>26.75</v>
       </c>
       <c r="E4" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>13244</v>
+        <v>21706</v>
       </c>
       <c r="B5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D5">
-        <v>72.25</v>
+        <v>963</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>13244</v>
+        <v>21707</v>
       </c>
       <c r="B6" t="s">
         <v>9</v>
@@ -509,10 +548,282 @@
         <v>1</v>
       </c>
       <c r="D6">
-        <v>578</v>
+        <v>1272</v>
       </c>
       <c r="E6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>21707</v>
+      </c>
+      <c r="B7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7">
+        <v>3</v>
+      </c>
+      <c r="D7">
+        <v>53</v>
+      </c>
+      <c r="E7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>21709</v>
+      </c>
+      <c r="B8" t="s">
         <v>10</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8">
+        <v>1132.5</v>
+      </c>
+      <c r="E8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>21709</v>
+      </c>
+      <c r="B9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9">
+        <v>3</v>
+      </c>
+      <c r="D9">
+        <v>37.75</v>
+      </c>
+      <c r="E9" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>21713</v>
+      </c>
+      <c r="B10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C10">
+        <v>1</v>
+      </c>
+      <c r="D10">
+        <v>630</v>
+      </c>
+      <c r="E10" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>21713</v>
+      </c>
+      <c r="B11" t="s">
+        <v>11</v>
+      </c>
+      <c r="C11">
+        <v>3</v>
+      </c>
+      <c r="D11">
+        <v>26.25</v>
+      </c>
+      <c r="E11" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>21745</v>
+      </c>
+      <c r="B12" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12">
+        <v>2</v>
+      </c>
+      <c r="D12">
+        <v>417.5</v>
+      </c>
+      <c r="E12" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>21752</v>
+      </c>
+      <c r="B13" t="s">
+        <v>13</v>
+      </c>
+      <c r="C13">
+        <v>2</v>
+      </c>
+      <c r="D13">
+        <v>474.25</v>
+      </c>
+      <c r="E13" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>21754</v>
+      </c>
+      <c r="B14" t="s">
+        <v>14</v>
+      </c>
+      <c r="C14">
+        <v>2</v>
+      </c>
+      <c r="D14">
+        <v>417.5</v>
+      </c>
+      <c r="E14" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>21771</v>
+      </c>
+      <c r="B15" t="s">
+        <v>15</v>
+      </c>
+      <c r="C15">
+        <v>2</v>
+      </c>
+      <c r="D15">
+        <v>417.5</v>
+      </c>
+      <c r="E15" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>21773</v>
+      </c>
+      <c r="B16" t="s">
+        <v>16</v>
+      </c>
+      <c r="C16">
+        <v>2</v>
+      </c>
+      <c r="D16">
+        <v>368.5</v>
+      </c>
+      <c r="E16" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17">
+        <v>21777</v>
+      </c>
+      <c r="B17" t="s">
+        <v>17</v>
+      </c>
+      <c r="C17">
+        <v>2</v>
+      </c>
+      <c r="D17">
+        <v>368.5</v>
+      </c>
+      <c r="E17" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18">
+        <v>21781</v>
+      </c>
+      <c r="B18" t="s">
+        <v>18</v>
+      </c>
+      <c r="C18">
+        <v>2</v>
+      </c>
+      <c r="D18">
+        <v>283</v>
+      </c>
+      <c r="E18" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19">
+        <v>21783</v>
+      </c>
+      <c r="B19" t="s">
+        <v>19</v>
+      </c>
+      <c r="C19">
+        <v>2</v>
+      </c>
+      <c r="D19">
+        <v>356.5</v>
+      </c>
+      <c r="E19" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20">
+        <v>21789</v>
+      </c>
+      <c r="B20" t="s">
+        <v>20</v>
+      </c>
+      <c r="C20">
+        <v>2</v>
+      </c>
+      <c r="D20">
+        <v>310</v>
+      </c>
+      <c r="E20" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21">
+        <v>22125</v>
+      </c>
+      <c r="B21" t="s">
+        <v>21</v>
+      </c>
+      <c r="C21">
+        <v>2</v>
+      </c>
+      <c r="D21">
+        <v>474.25</v>
+      </c>
+      <c r="E21" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22">
+        <v>22126</v>
+      </c>
+      <c r="B22" t="s">
+        <v>22</v>
+      </c>
+      <c r="C22">
+        <v>2</v>
+      </c>
+      <c r="D22">
+        <v>368.5</v>
+      </c>
+      <c r="E22" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>

--- a/Pricing Logic/modules/uploads/module_4_1126.xlsx
+++ b/Pricing Logic/modules/uploads/module_4_1126.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="9">
   <si>
     <t>Product ID</t>
   </si>
@@ -37,52 +37,7 @@
     <t>Tags</t>
   </si>
   <si>
-    <t>باندا مثلثات - 16 قطعه</t>
-  </si>
-  <si>
-    <t>باندا جورمية مثلثات - 8 قطعه</t>
-  </si>
-  <si>
-    <t>باندا جورمية مثلثات - 16 قطعه</t>
-  </si>
-  <si>
-    <t>باندا جورمية جبنة مربعات ب القشطة - 6 قطعه</t>
-  </si>
-  <si>
-    <t>ديرى مثلثات - 16 قطعه</t>
-  </si>
-  <si>
-    <t>جبنة باندا فيتا  - 500 جم</t>
-  </si>
-  <si>
-    <t>جبنة باندا رومى - 250 جم</t>
-  </si>
-  <si>
-    <t>جبنة باندا شيدر - 500 جم</t>
-  </si>
-  <si>
-    <t>جبنة باندا رومى - 500 جم</t>
-  </si>
-  <si>
-    <t>جبنة باندا شيدر  - 125 جم</t>
-  </si>
-  <si>
-    <t>جبنة باندا بسطرمة  - 125 جم</t>
-  </si>
-  <si>
-    <t>جبنة ديرى فيتا بلس  - 125 جم</t>
-  </si>
-  <si>
-    <t>جبنة ديرى فيتا  - 250 جم</t>
-  </si>
-  <si>
-    <t>جبنة ديرى فيتا بلس - 500 جم</t>
-  </si>
-  <si>
-    <t>جبنة باندا فيتا 250 جرام</t>
-  </si>
-  <si>
-    <t>جبنة باندا فيتا 125 جرام</t>
+    <t>صابون كامى رومانسية - 110 جم</t>
   </si>
   <si>
     <t>YES</t>
@@ -443,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -471,359 +426,36 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21705</v>
+        <v>8286</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2">
-        <v>870</v>
+        <v>58</v>
       </c>
       <c r="E2" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21705</v>
+        <v>8286</v>
       </c>
       <c r="B3" t="s">
         <v>7</v>
       </c>
       <c r="C3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D3">
-        <v>36.25</v>
+        <v>696</v>
       </c>
       <c r="E3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>21706</v>
-      </c>
-      <c r="B4" t="s">
         <v>8</v>
-      </c>
-      <c r="C4">
-        <v>3</v>
-      </c>
-      <c r="D4">
-        <v>26.75</v>
-      </c>
-      <c r="E4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>21706</v>
-      </c>
-      <c r="B5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5">
-        <v>963</v>
-      </c>
-      <c r="E5" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>21707</v>
-      </c>
-      <c r="B6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6">
-        <v>1</v>
-      </c>
-      <c r="D6">
-        <v>1272</v>
-      </c>
-      <c r="E6" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>21707</v>
-      </c>
-      <c r="B7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7">
-        <v>3</v>
-      </c>
-      <c r="D7">
-        <v>53</v>
-      </c>
-      <c r="E7" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>21709</v>
-      </c>
-      <c r="B8" t="s">
-        <v>10</v>
-      </c>
-      <c r="C8">
-        <v>1</v>
-      </c>
-      <c r="D8">
-        <v>1132.5</v>
-      </c>
-      <c r="E8" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>21709</v>
-      </c>
-      <c r="B9" t="s">
-        <v>10</v>
-      </c>
-      <c r="C9">
-        <v>3</v>
-      </c>
-      <c r="D9">
-        <v>37.75</v>
-      </c>
-      <c r="E9" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>21713</v>
-      </c>
-      <c r="B10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C10">
-        <v>1</v>
-      </c>
-      <c r="D10">
-        <v>630</v>
-      </c>
-      <c r="E10" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>21713</v>
-      </c>
-      <c r="B11" t="s">
-        <v>11</v>
-      </c>
-      <c r="C11">
-        <v>3</v>
-      </c>
-      <c r="D11">
-        <v>26.25</v>
-      </c>
-      <c r="E11" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>21745</v>
-      </c>
-      <c r="B12" t="s">
-        <v>12</v>
-      </c>
-      <c r="C12">
-        <v>2</v>
-      </c>
-      <c r="D12">
-        <v>417.5</v>
-      </c>
-      <c r="E12" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>21752</v>
-      </c>
-      <c r="B13" t="s">
-        <v>13</v>
-      </c>
-      <c r="C13">
-        <v>2</v>
-      </c>
-      <c r="D13">
-        <v>474.25</v>
-      </c>
-      <c r="E13" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>21754</v>
-      </c>
-      <c r="B14" t="s">
-        <v>14</v>
-      </c>
-      <c r="C14">
-        <v>2</v>
-      </c>
-      <c r="D14">
-        <v>417.5</v>
-      </c>
-      <c r="E14" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>21771</v>
-      </c>
-      <c r="B15" t="s">
-        <v>15</v>
-      </c>
-      <c r="C15">
-        <v>2</v>
-      </c>
-      <c r="D15">
-        <v>417.5</v>
-      </c>
-      <c r="E15" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>21773</v>
-      </c>
-      <c r="B16" t="s">
-        <v>16</v>
-      </c>
-      <c r="C16">
-        <v>2</v>
-      </c>
-      <c r="D16">
-        <v>368.5</v>
-      </c>
-      <c r="E16" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17">
-        <v>21777</v>
-      </c>
-      <c r="B17" t="s">
-        <v>17</v>
-      </c>
-      <c r="C17">
-        <v>2</v>
-      </c>
-      <c r="D17">
-        <v>368.5</v>
-      </c>
-      <c r="E17" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18">
-        <v>21781</v>
-      </c>
-      <c r="B18" t="s">
-        <v>18</v>
-      </c>
-      <c r="C18">
-        <v>2</v>
-      </c>
-      <c r="D18">
-        <v>283</v>
-      </c>
-      <c r="E18" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19">
-        <v>21783</v>
-      </c>
-      <c r="B19" t="s">
-        <v>19</v>
-      </c>
-      <c r="C19">
-        <v>2</v>
-      </c>
-      <c r="D19">
-        <v>356.5</v>
-      </c>
-      <c r="E19" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20">
-        <v>21789</v>
-      </c>
-      <c r="B20" t="s">
-        <v>20</v>
-      </c>
-      <c r="C20">
-        <v>2</v>
-      </c>
-      <c r="D20">
-        <v>310</v>
-      </c>
-      <c r="E20" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21">
-        <v>22125</v>
-      </c>
-      <c r="B21" t="s">
-        <v>21</v>
-      </c>
-      <c r="C21">
-        <v>2</v>
-      </c>
-      <c r="D21">
-        <v>474.25</v>
-      </c>
-      <c r="E21" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22">
-        <v>22126</v>
-      </c>
-      <c r="B22" t="s">
-        <v>22</v>
-      </c>
-      <c r="C22">
-        <v>2</v>
-      </c>
-      <c r="D22">
-        <v>368.5</v>
-      </c>
-      <c r="E22" t="s">
-        <v>23</v>
       </c>
     </row>
   </sheetData>

--- a/Pricing Logic/modules/uploads/module_4_1126.xlsx
+++ b/Pricing Logic/modules/uploads/module_4_1126.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="24">
   <si>
     <t>Product ID</t>
   </si>
@@ -37,7 +37,52 @@
     <t>Tags</t>
   </si>
   <si>
-    <t>صابون كامى رومانسية - 110 جم</t>
+    <t>زيت كريستال الممتاز خليط - 1 لتر</t>
+  </si>
+  <si>
+    <t>زيت كريستال الممتاز خليط - 700 مل</t>
+  </si>
+  <si>
+    <t>زيت ريحانة دوار الشمس بيور - 700 مل</t>
+  </si>
+  <si>
+    <t>زيت حبوبة خليط - 700 مل</t>
+  </si>
+  <si>
+    <t>زيت كريستال عباد الشمس 6 زجاجة - 700 مل</t>
+  </si>
+  <si>
+    <t>زيت كريستال عباد الشمس 6 زجاجة - 1.6 لتر</t>
+  </si>
+  <si>
+    <t>سندة زيت خليط - 1 لتر</t>
+  </si>
+  <si>
+    <t>زيت كريستال ذرة 6 زجاجة - 700 مل</t>
+  </si>
+  <si>
+    <t>زيت كريستال ذرة - 3.5 لتر</t>
+  </si>
+  <si>
+    <t>زيت حبوبة خليط - 540 مل</t>
+  </si>
+  <si>
+    <t>زيت كريستال عباد الشمس - 5 لتر</t>
+  </si>
+  <si>
+    <t>زيت حبوبة خليط - 1.8 لتر</t>
+  </si>
+  <si>
+    <t>زيت حبوبة خليط - 2.4 لتر</t>
+  </si>
+  <si>
+    <t>زيت كريستال ذرة 6 زجاجة - 1 لتر</t>
+  </si>
+  <si>
+    <t>زيت ثمرات خليط - 700 مل</t>
+  </si>
+  <si>
+    <t>زيت ثمرات خليط - 550 مل</t>
   </si>
   <si>
     <t>YES</t>
@@ -398,7 +443,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -426,36 +471,274 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>8286</v>
+        <v>9</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
       </c>
       <c r="C2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D2">
-        <v>58</v>
+        <v>866</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>8286</v>
+        <v>448</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C3">
         <v>1</v>
       </c>
       <c r="D3">
-        <v>696</v>
+        <v>625</v>
       </c>
       <c r="E3" t="s">
-        <v>8</v>
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>1448</v>
+      </c>
+      <c r="B4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>730.5</v>
+      </c>
+      <c r="E4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>1490</v>
+      </c>
+      <c r="B5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>604</v>
+      </c>
+      <c r="E5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>2878</v>
+      </c>
+      <c r="B6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6">
+        <v>388.25</v>
+      </c>
+      <c r="E6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>2935</v>
+      </c>
+      <c r="B7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7">
+        <v>892.5</v>
+      </c>
+      <c r="E7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>6497</v>
+      </c>
+      <c r="B8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8">
+        <v>855</v>
+      </c>
+      <c r="E8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>7324</v>
+      </c>
+      <c r="B9" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+      <c r="D9">
+        <v>480.5</v>
+      </c>
+      <c r="E9" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>7520</v>
+      </c>
+      <c r="B10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10">
+        <v>1</v>
+      </c>
+      <c r="D10">
+        <v>1464.75</v>
+      </c>
+      <c r="E10" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>8926</v>
+      </c>
+      <c r="B11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11">
+        <v>1</v>
+      </c>
+      <c r="D11">
+        <v>495</v>
+      </c>
+      <c r="E11" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>9070</v>
+      </c>
+      <c r="B12" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12">
+        <v>1</v>
+      </c>
+      <c r="D12">
+        <v>895</v>
+      </c>
+      <c r="E12" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>9358</v>
+      </c>
+      <c r="B13" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13">
+        <v>1</v>
+      </c>
+      <c r="D13">
+        <v>554</v>
+      </c>
+      <c r="E13" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>11402</v>
+      </c>
+      <c r="B14" t="s">
+        <v>19</v>
+      </c>
+      <c r="C14">
+        <v>1</v>
+      </c>
+      <c r="D14">
+        <v>704</v>
+      </c>
+      <c r="E14" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>11962</v>
+      </c>
+      <c r="B15" t="s">
+        <v>20</v>
+      </c>
+      <c r="C15">
+        <v>1</v>
+      </c>
+      <c r="D15">
+        <v>681.75</v>
+      </c>
+      <c r="E15" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>12924</v>
+      </c>
+      <c r="B16" t="s">
+        <v>21</v>
+      </c>
+      <c r="C16">
+        <v>1</v>
+      </c>
+      <c r="D16">
+        <v>600</v>
+      </c>
+      <c r="E16" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17">
+        <v>12925</v>
+      </c>
+      <c r="B17" t="s">
+        <v>22</v>
+      </c>
+      <c r="C17">
+        <v>1</v>
+      </c>
+      <c r="D17">
+        <v>490</v>
+      </c>
+      <c r="E17" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>

--- a/Pricing Logic/modules/uploads/module_4_1126.xlsx
+++ b/Pricing Logic/modules/uploads/module_4_1126.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="15">
   <si>
     <t>Product ID</t>
   </si>
@@ -37,52 +37,25 @@
     <t>Tags</t>
   </si>
   <si>
-    <t>زيت كريستال الممتاز خليط - 1 لتر</t>
-  </si>
-  <si>
-    <t>زيت كريستال الممتاز خليط - 700 مل</t>
-  </si>
-  <si>
-    <t>زيت ريحانة دوار الشمس بيور - 700 مل</t>
+    <t>زيت حبوبة خليط - 900 مل</t>
+  </si>
+  <si>
+    <t>جبنة دومتى فيتا بلس - 125 جم</t>
   </si>
   <si>
     <t>زيت حبوبة خليط - 700 مل</t>
   </si>
   <si>
-    <t>زيت كريستال عباد الشمس 6 زجاجة - 700 مل</t>
-  </si>
-  <si>
-    <t>زيت كريستال عباد الشمس 6 زجاجة - 1.6 لتر</t>
-  </si>
-  <si>
-    <t>سندة زيت خليط - 1 لتر</t>
-  </si>
-  <si>
-    <t>زيت كريستال ذرة 6 زجاجة - 700 مل</t>
-  </si>
-  <si>
-    <t>زيت كريستال ذرة - 3.5 لتر</t>
-  </si>
-  <si>
-    <t>زيت حبوبة خليط - 540 مل</t>
-  </si>
-  <si>
-    <t>زيت كريستال عباد الشمس - 5 لتر</t>
-  </si>
-  <si>
-    <t>زيت حبوبة خليط - 1.8 لتر</t>
+    <t>سندة زيت خليط - 700 مل</t>
+  </si>
+  <si>
+    <t>سندة زيت خليط - 900 مل</t>
   </si>
   <si>
     <t>زيت حبوبة خليط - 2.4 لتر</t>
   </si>
   <si>
-    <t>زيت كريستال ذرة 6 زجاجة - 1 لتر</t>
-  </si>
-  <si>
-    <t>زيت ثمرات خليط - 700 مل</t>
-  </si>
-  <si>
-    <t>زيت ثمرات خليط - 550 مل</t>
+    <t>دومتي جبنة فيتا بلس - 500 جم</t>
   </si>
   <si>
     <t>YES</t>
@@ -443,7 +416,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -471,7 +444,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>9</v>
+        <v>823</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
@@ -480,15 +453,15 @@
         <v>1</v>
       </c>
       <c r="D2">
-        <v>866</v>
+        <v>777</v>
       </c>
       <c r="E2" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>448</v>
+        <v>903</v>
       </c>
       <c r="B3" t="s">
         <v>8</v>
@@ -497,15 +470,15 @@
         <v>1</v>
       </c>
       <c r="D3">
-        <v>625</v>
+        <v>402</v>
       </c>
       <c r="E3" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>1448</v>
+        <v>1490</v>
       </c>
       <c r="B4" t="s">
         <v>9</v>
@@ -514,15 +487,15 @@
         <v>1</v>
       </c>
       <c r="D4">
-        <v>730.5</v>
+        <v>620</v>
       </c>
       <c r="E4" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>1490</v>
+        <v>6494</v>
       </c>
       <c r="B5" t="s">
         <v>10</v>
@@ -531,15 +504,15 @@
         <v>1</v>
       </c>
       <c r="D5">
-        <v>604</v>
+        <v>615</v>
       </c>
       <c r="E5" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>2878</v>
+        <v>6496</v>
       </c>
       <c r="B6" t="s">
         <v>11</v>
@@ -548,15 +521,15 @@
         <v>1</v>
       </c>
       <c r="D6">
-        <v>388.25</v>
+        <v>772</v>
       </c>
       <c r="E6" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>2935</v>
+        <v>11402</v>
       </c>
       <c r="B7" t="s">
         <v>12</v>
@@ -565,180 +538,27 @@
         <v>1</v>
       </c>
       <c r="D7">
-        <v>892.5</v>
+        <v>717</v>
       </c>
       <c r="E7" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>6497</v>
+        <v>19981</v>
       </c>
       <c r="B8" t="s">
         <v>13</v>
       </c>
       <c r="C8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D8">
-        <v>855</v>
+        <v>460</v>
       </c>
       <c r="E8" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>7324</v>
-      </c>
-      <c r="B9" t="s">
-        <v>14</v>
-      </c>
-      <c r="C9">
-        <v>1</v>
-      </c>
-      <c r="D9">
-        <v>480.5</v>
-      </c>
-      <c r="E9" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>7520</v>
-      </c>
-      <c r="B10" t="s">
-        <v>15</v>
-      </c>
-      <c r="C10">
-        <v>1</v>
-      </c>
-      <c r="D10">
-        <v>1464.75</v>
-      </c>
-      <c r="E10" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>8926</v>
-      </c>
-      <c r="B11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C11">
-        <v>1</v>
-      </c>
-      <c r="D11">
-        <v>495</v>
-      </c>
-      <c r="E11" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>9070</v>
-      </c>
-      <c r="B12" t="s">
-        <v>17</v>
-      </c>
-      <c r="C12">
-        <v>1</v>
-      </c>
-      <c r="D12">
-        <v>895</v>
-      </c>
-      <c r="E12" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>9358</v>
-      </c>
-      <c r="B13" t="s">
-        <v>18</v>
-      </c>
-      <c r="C13">
-        <v>1</v>
-      </c>
-      <c r="D13">
-        <v>554</v>
-      </c>
-      <c r="E13" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>11402</v>
-      </c>
-      <c r="B14" t="s">
-        <v>19</v>
-      </c>
-      <c r="C14">
-        <v>1</v>
-      </c>
-      <c r="D14">
-        <v>704</v>
-      </c>
-      <c r="E14" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>11962</v>
-      </c>
-      <c r="B15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C15">
-        <v>1</v>
-      </c>
-      <c r="D15">
-        <v>681.75</v>
-      </c>
-      <c r="E15" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>12924</v>
-      </c>
-      <c r="B16" t="s">
-        <v>21</v>
-      </c>
-      <c r="C16">
-        <v>1</v>
-      </c>
-      <c r="D16">
-        <v>600</v>
-      </c>
-      <c r="E16" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17">
-        <v>12925</v>
-      </c>
-      <c r="B17" t="s">
-        <v>22</v>
-      </c>
-      <c r="C17">
-        <v>1</v>
-      </c>
-      <c r="D17">
-        <v>490</v>
-      </c>
-      <c r="E17" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>

--- a/Pricing Logic/modules/uploads/module_4_1126.xlsx
+++ b/Pricing Logic/modules/uploads/module_4_1126.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>Product ID</t>
   </si>
@@ -37,25 +37,7 @@
     <t>Tags</t>
   </si>
   <si>
-    <t>زيت حبوبة خليط - 900 مل</t>
-  </si>
-  <si>
-    <t>جبنة دومتى فيتا بلس - 125 جم</t>
-  </si>
-  <si>
-    <t>زيت حبوبة خليط - 700 مل</t>
-  </si>
-  <si>
-    <t>سندة زيت خليط - 700 مل</t>
-  </si>
-  <si>
-    <t>سندة زيت خليط - 900 مل</t>
-  </si>
-  <si>
-    <t>زيت حبوبة خليط - 2.4 لتر</t>
-  </si>
-  <si>
-    <t>دومتي جبنة فيتا بلس - 500 جم</t>
+    <t>دومتي عصير مانجو- 1 لتر</t>
   </si>
   <si>
     <t>YES</t>
@@ -416,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -444,121 +426,19 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>823</v>
+        <v>3865</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2">
-        <v>777</v>
+        <v>290</v>
       </c>
       <c r="E2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>903</v>
-      </c>
-      <c r="B3" t="s">
         <v>8</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>402</v>
-      </c>
-      <c r="E3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>1490</v>
-      </c>
-      <c r="B4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="D4">
-        <v>620</v>
-      </c>
-      <c r="E4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>6494</v>
-      </c>
-      <c r="B5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5">
-        <v>615</v>
-      </c>
-      <c r="E5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>6496</v>
-      </c>
-      <c r="B6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C6">
-        <v>1</v>
-      </c>
-      <c r="D6">
-        <v>772</v>
-      </c>
-      <c r="E6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>11402</v>
-      </c>
-      <c r="B7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C7">
-        <v>1</v>
-      </c>
-      <c r="D7">
-        <v>717</v>
-      </c>
-      <c r="E7" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>19981</v>
-      </c>
-      <c r="B8" t="s">
-        <v>13</v>
-      </c>
-      <c r="C8">
-        <v>2</v>
-      </c>
-      <c r="D8">
-        <v>460</v>
-      </c>
-      <c r="E8" t="s">
-        <v>14</v>
       </c>
     </row>
   </sheetData>

--- a/Pricing Logic/modules/uploads/module_4_1126.xlsx
+++ b/Pricing Logic/modules/uploads/module_4_1126.xlsx
@@ -37,7 +37,7 @@
     <t>Tags</t>
   </si>
   <si>
-    <t>دومتي عصير مانجو- 1 لتر</t>
+    <t>سمن كريستال ابيض صفيحة - 4.25 كجم</t>
   </si>
   <si>
     <t>YES</t>
@@ -426,16 +426,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>3865</v>
+        <v>4926</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
       </c>
       <c r="C2">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D2">
-        <v>290</v>
+        <v>389.5</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
